--- a/SRMS_V5_TEST_PACK/subjects_import.xlsx
+++ b/SRMS_V5_TEST_PACK/subjects_import.xlsx
@@ -461,10 +461,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="94" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -486,7 +486,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SUBJECT REGISTRATION FORM</t>
+          <t>SUBJECT REGISTRATION FORM - MIXED CASES</t>
         </is>
       </c>
     </row>
@@ -501,21 +501,21 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1. Do not modify the column headers in Row 10.</t>
+          <t>1. Duplicate subject names are intentional so the conflict-update branch can be exercised.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2. Start data entry from Row 12 (below the sample row).</t>
+          <t>2. Include both O-Level and A-Level subjects in one file to test level-scoped imports.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3. Ensure the 'Admission No' exists in the system where required.</t>
+          <t>3. A repeated subject with a different type should update the existing row.</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COUNTED</t>
+          <t>PRINCIPAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kiswahili</t>
+          <t>English</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Kiswahili</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>History</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Civics</t>
+          <t>Geography</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -710,41 +710,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Civics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PRINCIPAL</t>
+          <t>COUNTED</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A_LEVEL</t>
+          <t>O_LEVEL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Geography</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRINCIPAL</t>
+          <t>COUNTED</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A_LEVEL</t>
+          <t>O_LEVEL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>History</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -761,15 +761,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A_LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A_LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>General Studies</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>SUBSIDIARY</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A_LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>General Studies</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A_LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>COUNTED</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>A_LEVEL</t>
         </is>
